--- a/gorevler/ekler/aicore-altyapi-gereksinimleri/AICore_Altyapi_Gereksinimleri.xlsx
+++ b/gorevler/ekler/aicore-altyapi-gereksinimleri/AICore_Altyapi_Gereksinimleri.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kademeler" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ortak Gereksinimler" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fiyat Modeli" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eklenti Notları" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notlar" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Kademeler" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Ortak Gereksinimler" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Fiyat Modeli" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Eklenti Notları" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Notlar" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -944,12 +944,12 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>SABİT (25)</t>
+          <t>SABİT (26)</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>KnowCoreAI · DocCoreAI · RootCoreAI · MergeCoreAI · ChatCoreAI · ClassifyCoreAI · PriorityCoreAI · ImpactCoreAI · PredictCoreAI · SentimentCoreAI · KBCoreAI · StormCoreAI · FlowCoreAI · DisCoreAI · TranslateCoreAI · VisionCoreAI · ShiftCoreAI · AuditCoreAI · AssetCoreAI · VendorCoreAI · ContractCoreAI · BudgetCoreAI · ProjectCoreAI · RisiCoreAI · GateCoreAI</t>
+          <t>KnowCoreAI · DocCoreAI · RootCoreAI · MergeCoreAI · ChatCoreAI · ClassifyCoreAI · PriorityCoreAI · ImpactCoreAI · PredictCoreAI · SentimentCoreAI · KBCoreAI · StormCoreAI · FlowCoreAI · DisCoreAI · TranslateCoreAI · VisionCoreAI · ShiftCoreAI · AuditCoreAI · AssetCoreAI · VendorCoreAI · ContractCoreAI · BudgetCoreAI · ProjectCoreAI · RisiCoreAI · GateCoreAI · TalentCoreAI</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>KARAR BEKLEYEN 5</t>
+          <t>KARAR BEKLEYEN 6</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1038,59 +1038,79 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr"/>
-      <c r="B18" s="3" t="inlineStr"/>
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>TalentCoreAI</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Kurum verisi üzerinde periyodik çalışır (sabit) — ama yönetim ekranı ReportCoreAI gibi yönetici koltuğuna da bağlanabilir (kişi başına).</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr"/>
+      <c r="B19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>NOT</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>GateCoreAI listeye eklendi (25.07): eklenti değil, kurumun kendi yapay zekâsının bağlandığı kapı. Kurum başına sabit; insansız biten iş ayrıca yıllık iş paketinden düşer.</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr"/>
-      <c r="B20" s="3" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>TalentCoreAI eklendi (14.10.2026): varsayılan kurala göre sabit gruba yazıldı; ticari tercih karar bekleyenlerde.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr"/>
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>Kaynak model: aicore/Yonetici_Ozeti_ve_Kararlar.md (25.07.2026). Sabit bedellerin rakamı sessiz ölçüm sonrası netleşir.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>PAKETLEME KURALI</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>Teklifte üç kalem vardır: (1) eklentiler — kişi başına ya da sabit, (2) GateCoreAI — zorunlu, kurum başına sabit, (3) kurulum + destek. Dördüncü kalem yoktur.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Eklentinin insansız çalışması eklentinin fiyatına DAHİLDİR; iş başına ayrıca ücret alınmaz. Aynı iş iki kez ücretlendirilmez.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>İş sayacı bir fatura kalemi değildir. İki işi vardır: müşterinin DIŞARIDAN bağladığı ajanların GateCoreAI bandını belirlemek ve kimliğini bildirmeyen otomasyonu yakalamak.</t>
+          <t>Teklifte üç kalem vardır: (1) eklentiler — kişi başına ya da sabit, (2) GateCoreAI — zorunlu, kurum başına sabit, (3) kurulum + destek. Dördüncü kalem yoktur.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Eklentinin insansız çalışması eklentinin fiyatına DAHİLDİR; iş başına ayrıca ücret alınmaz. Aynı iş iki kez ücretlendirilmez.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>İş sayacı bir fatura kalemi değildir. İki işi vardır: müşterinin DIŞARIDAN bağladığı ajanların GateCoreAI bandını belirlemek ve kimliğini bildirmeyen otomasyonu yakalamak.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>Kural tek cümle: lisansı olan iş sayılmaz, lisansı olmayan iş banda girer.</t>
         </is>
@@ -1107,7 +1127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2304,7 +2324,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>GateCoreAI</t>
         </is>
@@ -2337,6 +2357,43 @@
       <c r="G33" s="3" t="inlineStr">
         <is>
           <t>Eklenti değil, kurumun kendi yapay zekâsının bağlandığı kapı. Teknisyen sayısıyla ölçeklenmez; kurum başına yıllık sabit bedelle satılır. İnsansız biten iş ayrıca yıllık iş paketinden düşer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>TalentCoreAI</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Okur (kayıt geçmişi, çözüm süreleri, atama ve iş yükü verisi); atama, eğitim ve bilgi bankası ÖNERİSİ yazar (onay yönetimde)</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Eğitim, sertifika ve izin verisi (İK sistemi varsa entegrasyon)</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Periyodik analiz; atama önerisi kayıt başına</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Teknisyen sayısı + kayıt arşivi büyüklüğü</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>Sabit</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>Kurum verisi üzerinde periyodik çalışır, tek bir teknisyenin oturumuna bağlı değildir; ölçü teknisyen sayısı (ekip büyüklüğü). Yönetim ekranı yönetici koltuğuna da bağlanabilir: karar bekleyenler listesinde.</t>
         </is>
       </c>
     </row>
